--- a/Gravedigger2026/Assets/ConfigTables/Excel/制造_躯体外观配置表_Manufacture_BodyAppearanceConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Excel/制造_躯体外观配置表_Manufacture_BodyAppearanceConfig.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Work\Cursor\Gravedigger2026\Gravedigger2026\Gravedigger2026\Assets\ConfigTables\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\CursorGame_Git\Gravedigger2026\Gravedigger2026\Assets\ConfigTables\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12280"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="62">
   <si>
     <t>外观ID</t>
   </si>
@@ -230,14 +230,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -693,148 +686,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1187,9 +1180,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="5"/>
   <cols>
-    <col min="4" max="4" width="19.25" customWidth="1"/>
+    <col min="4" max="4" width="19.2545454545455" customWidth="1"/>
     <col min="5" max="5" width="20" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1269,9 +1262,6 @@
       <c r="E4" t="s">
         <v>22</v>
       </c>
-      <c r="F4" t="s">
-        <v>19</v>
-      </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" t="s">
@@ -1309,9 +1299,6 @@
       <c r="E6" t="s">
         <v>31</v>
       </c>
-      <c r="F6" t="s">
-        <v>19</v>
-      </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" t="s">
@@ -1329,9 +1316,6 @@
       <c r="E7" t="s">
         <v>36</v>
       </c>
-      <c r="F7" t="s">
-        <v>19</v>
-      </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" t="s">
@@ -1349,9 +1333,6 @@
       <c r="E8" t="s">
         <v>40</v>
       </c>
-      <c r="F8" t="s">
-        <v>19</v>
-      </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" t="s">
@@ -1369,9 +1350,6 @@
       <c r="E9" t="s">
         <v>44</v>
       </c>
-      <c r="F9" t="s">
-        <v>19</v>
-      </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" t="s">
@@ -1389,9 +1367,6 @@
       <c r="E10" t="s">
         <v>48</v>
       </c>
-      <c r="F10" t="s">
-        <v>19</v>
-      </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" t="s">
@@ -1409,9 +1384,6 @@
       <c r="E11" t="s">
         <v>53</v>
       </c>
-      <c r="F11" t="s">
-        <v>19</v>
-      </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" t="s">
@@ -1428,9 +1400,6 @@
       </c>
       <c r="E12" t="s">
         <v>57</v>
-      </c>
-      <c r="F12" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="13" spans="1:6">

--- a/Gravedigger2026/Assets/ConfigTables/Excel/制造_躯体外观配置表_Manufacture_BodyAppearanceConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Excel/制造_躯体外观配置表_Manufacture_BodyAppearanceConfig.xlsx
@@ -2,17 +2,17 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
-  <workbookPr/>
+  <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\CursorGame_Git\Gravedigger2026\Gravedigger2026\Assets\ConfigTables\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12280"/>
+    <workbookView windowWidth="25600" windowHeight="12080"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="BodyAppearanceConfig" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="64">
   <si>
     <t>外观ID</t>
   </si>
@@ -52,6 +52,12 @@
     <t>是否兜底</t>
   </si>
   <si>
+    <t>占地半径</t>
+  </si>
+  <si>
+    <t>朝向整圈翻转</t>
+  </si>
+  <si>
     <t>主键；→ Prefabs/Defend/Warriors/{AppearanceId}.prefab</t>
   </si>
   <si>
@@ -70,6 +76,12 @@
     <t>1=兜底外观</t>
   </si>
   <si>
+    <t>士兵 XZ 占地圆；缺省 0.1</t>
+  </si>
+  <si>
+    <t>0不转;1=(DirIndex+4)%8;缺省0</t>
+  </si>
+  <si>
     <t>AppearanceId</t>
   </si>
   <si>
@@ -88,12 +100,15 @@
     <t>IsFallback</t>
   </si>
   <si>
+    <t>BodyRadius</t>
+  </si>
+  <si>
+    <t>FacingYawFlip</t>
+  </si>
+  <si>
     <t>App_01</t>
   </si>
   <si>
-    <t>1</t>
-  </si>
-  <si>
     <t>Race_Human</t>
   </si>
   <si>
@@ -103,12 +118,12 @@
     <t>人类战士外观</t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
     <t>App_02</t>
   </si>
   <si>
-    <t>2</t>
-  </si>
-  <si>
     <t>Race_Construct</t>
   </si>
   <si>
@@ -133,9 +148,6 @@
     <t>App_04</t>
   </si>
   <si>
-    <t>3</t>
-  </si>
-  <si>
     <t>Race_Orc</t>
   </si>
   <si>
@@ -184,9 +196,6 @@
     <t>App_08</t>
   </si>
   <si>
-    <t>4</t>
-  </si>
-  <si>
     <t>Race_Demon</t>
   </si>
   <si>
@@ -212,9 +221,6 @@
   </si>
   <si>
     <t>Race_Beast</t>
-  </si>
-  <si>
-    <t/>
   </si>
   <si>
     <t>野兽保底外形</t>
@@ -230,7 +236,14 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -686,148 +699,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -885,7 +898,7 @@
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -969,6 +982,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -1003,6 +1017,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -1037,20 +1052,16 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
+                <a:tint val="100000"/>
+                <a:shade val="100000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:tint val="50000"/>
+                <a:shade val="100000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -1172,21 +1183,56 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:spDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </a:style>
+    </a:spDef>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="5"/>
-  <cols>
-    <col min="4" max="4" width="19.2545454545455" customWidth="1"/>
-    <col min="5" max="5" width="20" customWidth="1"/>
-  </cols>
+  <dimension ref="A1:H13"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="7"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:8">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1205,225 +1251,331 @@
       <c r="F1" t="s">
         <v>5</v>
       </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F2" t="s">
-        <v>11</v>
+        <v>13</v>
+      </c>
+      <c r="G2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" t="s">
+        <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D3" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E3" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F3" t="s">
-        <v>17</v>
+        <v>21</v>
+      </c>
+      <c r="G3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H3" t="s">
+        <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B4" t="s">
-        <v>19</v>
+        <v>24</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D4" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="E4" t="s">
-        <v>22</v>
+        <v>27</v>
+      </c>
+      <c r="F4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G4">
+        <v>0.16</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>23</v>
-      </c>
-      <c r="B5" t="s">
-        <v>24</v>
+        <v>29</v>
+      </c>
+      <c r="B5">
+        <v>2</v>
       </c>
       <c r="C5" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D5" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="E5" t="s">
-        <v>27</v>
-      </c>
-      <c r="F5" t="s">
-        <v>19</v>
+        <v>32</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5">
+        <v>0.16</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:8">
       <c r="A6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6">
+        <v>2</v>
+      </c>
+      <c r="C6" t="s">
+        <v>34</v>
+      </c>
+      <c r="D6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E6" t="s">
+        <v>36</v>
+      </c>
+      <c r="F6" t="s">
         <v>28</v>
       </c>
-      <c r="B6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C6" t="s">
-        <v>29</v>
-      </c>
-      <c r="D6" t="s">
-        <v>30</v>
-      </c>
-      <c r="E6" t="s">
-        <v>31</v>
+      <c r="G6">
+        <v>0.16</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>32</v>
-      </c>
-      <c r="B7" t="s">
-        <v>33</v>
+        <v>37</v>
+      </c>
+      <c r="B7">
+        <v>3</v>
       </c>
       <c r="C7" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="E7" t="s">
-        <v>36</v>
+        <v>40</v>
+      </c>
+      <c r="F7" t="s">
+        <v>28</v>
+      </c>
+      <c r="G7">
+        <v>0.16</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>37</v>
-      </c>
-      <c r="B8" t="s">
-        <v>24</v>
+        <v>41</v>
+      </c>
+      <c r="B8">
+        <v>2</v>
       </c>
       <c r="C8" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D8" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="E8" t="s">
-        <v>40</v>
+        <v>44</v>
+      </c>
+      <c r="F8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G8">
+        <v>0.16</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:8">
       <c r="A9" t="s">
-        <v>41</v>
-      </c>
-      <c r="B9" t="s">
-        <v>33</v>
+        <v>45</v>
+      </c>
+      <c r="B9">
+        <v>3</v>
       </c>
       <c r="C9" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="D9" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="E9" t="s">
-        <v>44</v>
+        <v>48</v>
+      </c>
+      <c r="F9" t="s">
+        <v>28</v>
+      </c>
+      <c r="G9">
+        <v>0.16</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:8">
       <c r="A10" t="s">
-        <v>45</v>
-      </c>
-      <c r="B10" t="s">
-        <v>19</v>
+        <v>49</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
       </c>
       <c r="C10" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D10" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="E10" t="s">
-        <v>48</v>
+        <v>52</v>
+      </c>
+      <c r="F10" t="s">
+        <v>28</v>
+      </c>
+      <c r="G10">
+        <v>0.16</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:8">
       <c r="A11" t="s">
-        <v>49</v>
-      </c>
-      <c r="B11" t="s">
-        <v>50</v>
+        <v>53</v>
+      </c>
+      <c r="B11">
+        <v>4</v>
       </c>
       <c r="C11" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D11" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="E11" t="s">
-        <v>53</v>
+        <v>56</v>
+      </c>
+      <c r="F11" t="s">
+        <v>28</v>
+      </c>
+      <c r="G11">
+        <v>0.16</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:8">
       <c r="A12" t="s">
-        <v>54</v>
-      </c>
-      <c r="B12" t="s">
-        <v>33</v>
+        <v>57</v>
+      </c>
+      <c r="B12">
+        <v>3</v>
       </c>
       <c r="C12" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D12" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="E12" t="s">
-        <v>57</v>
+        <v>60</v>
+      </c>
+      <c r="F12" t="s">
+        <v>28</v>
+      </c>
+      <c r="G12">
+        <v>0.16</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:8">
       <c r="A13" t="s">
-        <v>58</v>
-      </c>
-      <c r="B13" t="s">
-        <v>24</v>
+        <v>61</v>
+      </c>
+      <c r="B13">
+        <v>2</v>
       </c>
       <c r="C13" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D13" t="s">
-        <v>60</v>
+        <v>28</v>
       </c>
       <c r="E13" t="s">
-        <v>61</v>
-      </c>
-      <c r="F13" t="s">
-        <v>19</v>
+        <v>63</v>
+      </c>
+      <c r="F13">
+        <v>1</v>
+      </c>
+      <c r="G13">
+        <v>0.16</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
+  <ignoredErrors>
+    <ignoredError sqref="A1:G3 A4:F13" numberStoredAsText="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
--- a/Gravedigger2026/Assets/ConfigTables/Excel/制造_躯体外观配置表_Manufacture_BodyAppearanceConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Excel/制造_躯体外观配置表_Manufacture_BodyAppearanceConfig.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\CursorGame_Git\Gravedigger2026\Gravedigger2026\Assets\ConfigTables\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="f:\CursorGame_Git\Gravedigger2026\Gravedigger2026\Assets\ConfigTables\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC9CD208-6C47-4E3B-A7EC-F678D4D77B46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12080"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BodyAppearanceConfig" sheetId="1" r:id="rId1"/>
@@ -32,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="78">
   <si>
     <t>外观ID</t>
   </si>
@@ -223,20 +224,60 @@
     <t>Race_Beast</t>
   </si>
   <si>
-    <t>野兽保底外形</t>
+    <t>App_90</t>
+  </si>
+  <si>
+    <t>App_91</t>
+  </si>
+  <si>
+    <t>种族保底外形</t>
+  </si>
+  <si>
+    <t>App_92</t>
+  </si>
+  <si>
+    <t>App_93</t>
+  </si>
+  <si>
+    <t>App_94</t>
+  </si>
+  <si>
+    <t>App_95</t>
+  </si>
+  <si>
+    <t>App_96</t>
+  </si>
+  <si>
+    <t>App_97</t>
+  </si>
+  <si>
+    <t>App_98</t>
+  </si>
+  <si>
+    <t>App_99</t>
+  </si>
+  <si>
+    <t>野兽外观</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>构造体保底外形</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Race_Beast</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>野兽种族保底外形</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="21">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -252,151 +293,13 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
+      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="33">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -405,192 +308,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -598,310 +321,26 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1223,16 +662,16 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:H13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="7"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:H23"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1258,7 +697,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -1284,33 +723,33 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
-      <c r="A3" t="s">
+    <row r="3" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G3" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="H3" t="s">
+      <c r="H3" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>24</v>
       </c>
@@ -1336,7 +775,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>29</v>
       </c>
@@ -1352,9 +791,6 @@
       <c r="E5" t="s">
         <v>32</v>
       </c>
-      <c r="F5">
-        <v>1</v>
-      </c>
       <c r="G5">
         <v>0.16</v>
       </c>
@@ -1362,7 +798,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>33</v>
       </c>
@@ -1388,7 +824,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>37</v>
       </c>
@@ -1414,7 +850,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>41</v>
       </c>
@@ -1440,7 +876,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>45</v>
       </c>
@@ -1466,7 +902,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>49</v>
       </c>
@@ -1492,7 +928,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>53</v>
       </c>
@@ -1518,7 +954,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>57</v>
       </c>
@@ -1544,7 +980,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>61</v>
       </c>
@@ -1554,28 +990,252 @@
       <c r="C13" t="s">
         <v>62</v>
       </c>
-      <c r="D13" t="s">
-        <v>28</v>
-      </c>
       <c r="E13" t="s">
+        <v>74</v>
+      </c>
+      <c r="G13">
+        <v>0.16</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
         <v>63</v>
       </c>
-      <c r="F13">
-        <v>1</v>
-      </c>
-      <c r="G13">
-        <v>0.16</v>
-      </c>
-      <c r="H13">
+      <c r="B14">
+        <v>1</v>
+      </c>
+      <c r="C14" t="s">
+        <v>30</v>
+      </c>
+      <c r="E14" t="s">
+        <v>75</v>
+      </c>
+      <c r="F14">
+        <v>1</v>
+      </c>
+      <c r="G14">
+        <v>0.16</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>64</v>
+      </c>
+      <c r="B15">
+        <v>1</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E15" t="s">
+        <v>65</v>
+      </c>
+      <c r="F15">
+        <v>1</v>
+      </c>
+      <c r="G15">
+        <v>0.16</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>66</v>
+      </c>
+      <c r="B16">
+        <v>1</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E16" t="s">
+        <v>65</v>
+      </c>
+      <c r="F16">
+        <v>1</v>
+      </c>
+      <c r="G16">
+        <v>0.16</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>67</v>
+      </c>
+      <c r="B17">
+        <v>1</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E17" t="s">
+        <v>65</v>
+      </c>
+      <c r="F17">
+        <v>1</v>
+      </c>
+      <c r="G17">
+        <v>0.16</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>68</v>
+      </c>
+      <c r="B18">
+        <v>1</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E18" t="s">
+        <v>65</v>
+      </c>
+      <c r="F18">
+        <v>1</v>
+      </c>
+      <c r="G18">
+        <v>0.16</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>69</v>
+      </c>
+      <c r="B19">
+        <v>1</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E19" t="s">
+        <v>65</v>
+      </c>
+      <c r="F19">
+        <v>1</v>
+      </c>
+      <c r="G19">
+        <v>0.16</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>70</v>
+      </c>
+      <c r="B20">
+        <v>1</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E20" t="s">
+        <v>65</v>
+      </c>
+      <c r="F20">
+        <v>1</v>
+      </c>
+      <c r="G20">
+        <v>0.16</v>
+      </c>
+      <c r="H20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>71</v>
+      </c>
+      <c r="B21">
+        <v>1</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E21" t="s">
+        <v>65</v>
+      </c>
+      <c r="F21">
+        <v>1</v>
+      </c>
+      <c r="G21">
+        <v>0.16</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>72</v>
+      </c>
+      <c r="B22">
+        <v>1</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E22" t="s">
+        <v>65</v>
+      </c>
+      <c r="F22">
+        <v>1</v>
+      </c>
+      <c r="G22">
+        <v>0.16</v>
+      </c>
+      <c r="H22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>73</v>
+      </c>
+      <c r="B23">
+        <v>1</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E23" t="s">
+        <v>77</v>
+      </c>
+      <c r="F23">
+        <v>1</v>
+      </c>
+      <c r="G23">
+        <v>0.16</v>
+      </c>
+      <c r="H23">
         <v>0</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="A1:G3 A4:F13" numberStoredAsText="1"/>
+    <ignoredError sqref="A4:F4 A5:E5 A6:F12 A1:G2 A3:B3 D3:G3 A13:C13" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Gravedigger2026/Assets/ConfigTables/Excel/制造_躯体外观配置表_Manufacture_BodyAppearanceConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Excel/制造_躯体外观配置表_Manufacture_BodyAppearanceConfig.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="f:\CursorGame_Git\Gravedigger2026\Gravedigger2026\Assets\ConfigTables\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Work\Cursor\Gravedigger2026\Gravedigger2026\Gravedigger2026\Assets\ConfigTables\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC9CD208-6C47-4E3B-A7EC-F678D4D77B46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="BodyAppearanceConfig" sheetId="1" r:id="rId1"/>
@@ -33,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="81">
   <si>
     <t>外观ID</t>
   </si>
@@ -56,6 +55,12 @@
     <t>占地半径</t>
   </si>
   <si>
+    <t>推开系数</t>
+  </si>
+  <si>
+    <t>排斥强度系数</t>
+  </si>
+  <si>
     <t>朝向整圈翻转</t>
   </si>
   <si>
@@ -80,6 +85,12 @@
     <t>士兵 XZ 占地圆；缺省 0.1</t>
   </si>
   <si>
+    <t>≥0；缺省 1；SoftCollision 排斥冲量缩放（邻域贡献×对方系数）；不改变占地圆</t>
+  </si>
+  <si>
+    <t>≥0；缺省 1；SoftCollision 单体排斥（有效=全局×本系数）；Register 注入</t>
+  </si>
+  <si>
     <t>0不转;1=(DirIndex+4)%8;缺省0</t>
   </si>
   <si>
@@ -104,6 +115,12 @@
     <t>BodyRadius</t>
   </si>
   <si>
+    <t>PushCoefficient</t>
+  </si>
+  <si>
+    <t>RepulsionScale</t>
+  </si>
+  <si>
     <t>FacingYawFlip</t>
   </si>
   <si>
@@ -119,9 +136,6 @@
     <t>人类战士外观</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>App_02</t>
   </si>
   <si>
@@ -224,6 +238,9 @@
     <t>Race_Beast</t>
   </si>
   <si>
+    <t>野兽外观</t>
+  </si>
+  <si>
     <t>App_90</t>
   </si>
   <si>
@@ -257,27 +274,20 @@
     <t>App_99</t>
   </si>
   <si>
-    <t>野兽外观</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>构造体保底外形</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Race_Beast</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>野兽种族保底外形</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="21">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -293,13 +303,151 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -312,8 +460,194 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -321,26 +655,312 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -662,16 +1282,16 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H23"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:J23"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -696,322 +1316,376 @@
       <c r="H1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="I2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" spans="1:10">
       <c r="A3" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="H3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I3" t="s">
+        <v>28</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="B4">
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="D4" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E4" t="s">
-        <v>27</v>
-      </c>
-      <c r="F4" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="G4">
         <v>0.16</v>
       </c>
       <c r="H4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+        <v>0.5</v>
+      </c>
+      <c r="I4">
+        <v>0.5</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="B5">
         <v>2</v>
       </c>
       <c r="C5" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D5" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="E5" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="G5">
         <v>0.16</v>
       </c>
       <c r="H5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+        <v>0.5</v>
+      </c>
+      <c r="I5">
+        <v>0.5</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="B6">
         <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D6" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E6" t="s">
-        <v>36</v>
-      </c>
-      <c r="F6" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="G6">
         <v>0.16</v>
       </c>
       <c r="H6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+        <v>0.5</v>
+      </c>
+      <c r="I6">
+        <v>0.5</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B7">
         <v>3</v>
       </c>
       <c r="C7" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D7" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E7" t="s">
-        <v>40</v>
-      </c>
-      <c r="F7" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="G7">
         <v>0.16</v>
       </c>
       <c r="H7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+        <v>0.5</v>
+      </c>
+      <c r="I7">
+        <v>0.5</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="B8">
         <v>2</v>
       </c>
       <c r="C8" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D8" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="E8" t="s">
-        <v>44</v>
-      </c>
-      <c r="F8" t="s">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="G8">
         <v>0.16</v>
       </c>
       <c r="H8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+        <v>0.5</v>
+      </c>
+      <c r="I8">
+        <v>0.5</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
       <c r="A9" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B9">
         <v>3</v>
       </c>
       <c r="C9" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="D9" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="E9" t="s">
-        <v>48</v>
-      </c>
-      <c r="F9" t="s">
-        <v>28</v>
+        <v>53</v>
       </c>
       <c r="G9">
         <v>0.16</v>
       </c>
       <c r="H9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+        <v>0.5</v>
+      </c>
+      <c r="I9">
+        <v>0.5</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
       <c r="A10" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="B10">
         <v>1</v>
       </c>
       <c r="C10" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="D10" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="E10" t="s">
-        <v>52</v>
-      </c>
-      <c r="F10" t="s">
-        <v>28</v>
+        <v>57</v>
       </c>
       <c r="G10">
         <v>0.16</v>
       </c>
       <c r="H10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+        <v>0.5</v>
+      </c>
+      <c r="I10">
+        <v>0.5</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
       <c r="A11" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="B11">
         <v>4</v>
       </c>
       <c r="C11" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="D11" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="E11" t="s">
-        <v>56</v>
-      </c>
-      <c r="F11" t="s">
-        <v>28</v>
+        <v>61</v>
       </c>
       <c r="G11">
         <v>0.16</v>
       </c>
       <c r="H11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+        <v>0.5</v>
+      </c>
+      <c r="I11">
+        <v>0.5</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
       <c r="A12" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="B12">
         <v>3</v>
       </c>
       <c r="C12" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="D12" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="E12" t="s">
-        <v>60</v>
-      </c>
-      <c r="F12" t="s">
-        <v>28</v>
+        <v>65</v>
       </c>
       <c r="G12">
         <v>0.16</v>
       </c>
       <c r="H12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+        <v>0.5</v>
+      </c>
+      <c r="I12">
+        <v>0.5</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
       <c r="A13" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="B13">
         <v>2</v>
       </c>
       <c r="C13" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="E13" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="G13">
         <v>0.16</v>
       </c>
       <c r="H13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+        <v>0.5</v>
+      </c>
+      <c r="I13">
+        <v>0.5</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
       <c r="A14" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="B14">
         <v>1</v>
       </c>
       <c r="C14" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="E14" t="s">
-        <v>75</v>
+        <v>37</v>
       </c>
       <c r="F14">
         <v>1</v>
@@ -1020,21 +1694,27 @@
         <v>0.16</v>
       </c>
       <c r="H14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+        <v>0.5</v>
+      </c>
+      <c r="I14">
+        <v>0.5</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
       <c r="A15" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="B15">
         <v>1</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="E15" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="F15">
         <v>1</v>
@@ -1043,21 +1723,27 @@
         <v>0.16</v>
       </c>
       <c r="H15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+        <v>0.5</v>
+      </c>
+      <c r="I15">
+        <v>0.5</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
       <c r="A16" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="B16">
         <v>1</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="E16" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="F16">
         <v>1</v>
@@ -1066,21 +1752,27 @@
         <v>0.16</v>
       </c>
       <c r="H16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+        <v>0.5</v>
+      </c>
+      <c r="I16">
+        <v>0.5</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
       <c r="A17" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="B17">
         <v>1</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="E17" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="F17">
         <v>1</v>
@@ -1089,21 +1781,27 @@
         <v>0.16</v>
       </c>
       <c r="H17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+        <v>0.5</v>
+      </c>
+      <c r="I17">
+        <v>0.5</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
       <c r="A18" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="B18">
         <v>1</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="E18" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="F18">
         <v>1</v>
@@ -1112,21 +1810,27 @@
         <v>0.16</v>
       </c>
       <c r="H18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+        <v>0.5</v>
+      </c>
+      <c r="I18">
+        <v>0.5</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
       <c r="A19" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="B19">
         <v>1</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="E19" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="F19">
         <v>1</v>
@@ -1135,21 +1839,27 @@
         <v>0.16</v>
       </c>
       <c r="H19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+        <v>0.5</v>
+      </c>
+      <c r="I19">
+        <v>0.5</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
       <c r="A20" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="B20">
         <v>1</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="E20" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="F20">
         <v>1</v>
@@ -1158,21 +1868,27 @@
         <v>0.16</v>
       </c>
       <c r="H20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+        <v>0.5</v>
+      </c>
+      <c r="I20">
+        <v>0.5</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
       <c r="A21" t="s">
+        <v>77</v>
+      </c>
+      <c r="B21">
+        <v>1</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E21" t="s">
         <v>71</v>
-      </c>
-      <c r="B21">
-        <v>1</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E21" t="s">
-        <v>65</v>
       </c>
       <c r="F21">
         <v>1</v>
@@ -1181,21 +1897,27 @@
         <v>0.16</v>
       </c>
       <c r="H21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+        <v>0.5</v>
+      </c>
+      <c r="I21">
+        <v>0.5</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
       <c r="A22" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="B22">
         <v>1</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="E22" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="F22">
         <v>1</v>
@@ -1204,21 +1926,27 @@
         <v>0.16</v>
       </c>
       <c r="H22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+        <v>0.5</v>
+      </c>
+      <c r="I22">
+        <v>0.5</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
       <c r="A23" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="B23">
         <v>1</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="E23" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F23">
         <v>1</v>
@@ -1227,15 +1955,18 @@
         <v>0.16</v>
       </c>
       <c r="H23">
+        <v>0.5</v>
+      </c>
+      <c r="I23">
+        <v>0.5</v>
+      </c>
+      <c r="J23">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <ignoredErrors>
-    <ignoredError sqref="A4:F4 A5:E5 A6:F12 A1:G2 A3:B3 D3:G3 A13:C13" numberStoredAsText="1"/>
-  </ignoredErrors>
+  <headerFooter/>
 </worksheet>
 </file>